--- a/artfynd/A 37651-2025 artfynd.xlsx
+++ b/artfynd/A 37651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86704824</v>
+        <v>132349696</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärnåsen, Hjd</t>
+          <t>Starrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413865.1447574114</v>
+        <v>413781</v>
       </c>
       <c r="R2" t="n">
-        <v>6973014.774468095</v>
+        <v>6972893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,22 +754,326 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132349430</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Starrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>413976</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6972729</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132349700</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Starrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>413781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6972893</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86704824</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärnåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413865</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6973015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 37651-2025 artfynd.xlsx
+++ b/artfynd/A 37651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349430</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349700</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86704824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>